--- a/data/RGPV_Result_0105IT2410_1-20.xlsx
+++ b/data/RGPV_Result_0105IT2410_1-20.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,6 +31,10 @@
     <font>
       <b val="1"/>
       <color rgb="00008000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -65,13 +69,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -455,7 +460,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="17" max="17"/>
     <col width="8" customWidth="1" min="18" max="18"/>
   </cols>
@@ -651,22 +656,112 @@
           <t>0105IT241002</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>AAYUSH MEHRA</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>Fail in IT305</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>5.71</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>0105IT241003</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
